--- a/data/trans_bre/P8_2_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P8_2_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 19,5</t>
+          <t>12,06; 19,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,31; 20,11</t>
+          <t>11,17; 19,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 19,92</t>
+          <t>10,66; 20,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 23,42</t>
+          <t>13,6; 23,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,93; 71,68</t>
+          <t>38,21; 71,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,96; 65,64</t>
+          <t>30,88; 63,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,24; 64,34</t>
+          <t>30,27; 65,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,93; 72,61</t>
+          <t>34,69; 73,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,79</t>
+          <t>0,03; 3,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,99</t>
+          <t>1,48; 5,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,46</t>
+          <t>2,22; 6,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 1,46</t>
+          <t>-29,57; 1,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 64,84</t>
+          <t>0,04; 62,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 75,9</t>
+          <t>15,26; 72,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 75,43</t>
+          <t>21,35; 76,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 12,2</t>
+          <t>-71,94; 10,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,33</t>
+          <t>0,27; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,95</t>
+          <t>-2,82; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,25</t>
+          <t>-2,86; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,95</t>
+          <t>-0,17; 4,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 155,8</t>
+          <t>2,5; 152,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 90,43</t>
+          <t>-31,09; 85,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 69,56</t>
+          <t>-29,77; 74,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 92,87</t>
+          <t>-3,21; 92,9</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,12</t>
+          <t>7,27; 11,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,23</t>
+          <t>8,23; 12,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,24</t>
+          <t>6,32; 10,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 6,83</t>
+          <t>-19,08; 7,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,68; 84,71</t>
+          <t>48,79; 84,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 85,18</t>
+          <t>49,16; 81,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,65; 74,9</t>
+          <t>40,52; 74,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 44,9</t>
+          <t>-48,96; 45,74</t>
         </is>
       </c>
     </row>
